--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テンプレート" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="テンプレート" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -318,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -687,6 +687,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top style="medium"/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium"/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -698,7 +752,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="198">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1252,6 +1306,25 @@
     <xf numFmtId="168" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1977,7 +2050,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="132" t="n"/>
-      <c r="C11" s="139" t="n"/>
+      <c r="C11" s="129" t="n"/>
       <c r="D11" s="120" t="n"/>
       <c r="E11" s="130" t="n"/>
       <c r="F11" s="131" t="n"/>
@@ -2013,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="132" t="n"/>
-      <c r="C12" s="139" t="n"/>
+      <c r="C12" s="129" t="n"/>
       <c r="D12" s="120" t="n"/>
       <c r="E12" s="130" t="n"/>
       <c r="F12" s="131" t="n"/>
@@ -2085,7 +2158,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="132" t="n"/>
-      <c r="C14" s="139" t="n"/>
+      <c r="C14" s="129" t="n"/>
       <c r="D14" s="120" t="n"/>
       <c r="E14" s="130" t="n"/>
       <c r="F14" s="131" t="n"/>
@@ -2121,7 +2194,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="132" t="n"/>
-      <c r="C15" s="139" t="n"/>
+      <c r="C15" s="129" t="n"/>
       <c r="D15" s="120" t="n"/>
       <c r="E15" s="130" t="n"/>
       <c r="F15" s="131" t="n"/>
@@ -2157,7 +2230,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="132" t="n"/>
-      <c r="C16" s="139" t="n"/>
+      <c r="C16" s="129" t="n"/>
       <c r="D16" s="120" t="n"/>
       <c r="E16" s="130" t="n"/>
       <c r="F16" s="131" t="n"/>
@@ -2337,7 +2410,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="132" t="n"/>
-      <c r="C21" s="139" t="n"/>
+      <c r="C21" s="129" t="n"/>
       <c r="D21" s="120" t="n"/>
       <c r="E21" s="130" t="n"/>
       <c r="F21" s="131" t="n"/>
@@ -2373,7 +2446,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="132" t="n"/>
-      <c r="C22" s="139" t="n"/>
+      <c r="C22" s="129" t="n"/>
       <c r="D22" s="120" t="n"/>
       <c r="E22" s="130" t="n"/>
       <c r="F22" s="131" t="n"/>
@@ -2620,7 +2693,15 @@
     </row>
     <row r="29" ht="27" customHeight="1" s="92">
       <c r="A29" s="93" t="n"/>
-      <c r="B29" s="172" t="n"/>
+      <c r="B29" s="187" t="n"/>
+      <c r="C29" s="188" t="n"/>
+      <c r="D29" s="188" t="n"/>
+      <c r="E29" s="188" t="n"/>
+      <c r="F29" s="188" t="n"/>
+      <c r="G29" s="188" t="n"/>
+      <c r="H29" s="188" t="n"/>
+      <c r="I29" s="188" t="n"/>
+      <c r="J29" s="189" t="n"/>
       <c r="K29" s="173" t="inlineStr">
         <is>
           <t>山本</t>
@@ -2647,6 +2728,15 @@
     </row>
     <row r="30" ht="27" customHeight="1" s="92">
       <c r="A30" s="93" t="n"/>
+      <c r="B30" s="190" t="n"/>
+      <c r="C30" s="191" t="n"/>
+      <c r="D30" s="191" t="n"/>
+      <c r="E30" s="191" t="n"/>
+      <c r="F30" s="191" t="n"/>
+      <c r="G30" s="191" t="n"/>
+      <c r="H30" s="191" t="n"/>
+      <c r="I30" s="191" t="n"/>
+      <c r="J30" s="192" t="n"/>
       <c r="K30" s="175" t="inlineStr">
         <is>
           <t>熱田</t>
@@ -2673,6 +2763,15 @@
     </row>
     <row r="31" ht="27" customHeight="1" s="92">
       <c r="A31" s="93" t="n"/>
+      <c r="B31" s="190" t="n"/>
+      <c r="C31" s="191" t="n"/>
+      <c r="D31" s="191" t="n"/>
+      <c r="E31" s="191" t="n"/>
+      <c r="F31" s="191" t="n"/>
+      <c r="G31" s="191" t="n"/>
+      <c r="H31" s="191" t="n"/>
+      <c r="I31" s="191" t="n"/>
+      <c r="J31" s="192" t="n"/>
       <c r="K31" s="176" t="inlineStr">
         <is>
           <t>安保</t>
@@ -2699,6 +2798,15 @@
     </row>
     <row r="32" ht="27" customHeight="1" s="92">
       <c r="A32" s="93" t="n"/>
+      <c r="B32" s="190" t="n"/>
+      <c r="C32" s="191" t="n"/>
+      <c r="D32" s="191" t="n"/>
+      <c r="E32" s="191" t="n"/>
+      <c r="F32" s="191" t="n"/>
+      <c r="G32" s="191" t="n"/>
+      <c r="H32" s="191" t="n"/>
+      <c r="I32" s="191" t="n"/>
+      <c r="J32" s="192" t="n"/>
       <c r="K32" s="177" t="n">
         <v>0</v>
       </c>
@@ -2720,6 +2828,15 @@
     </row>
     <row r="33" ht="27" customHeight="1" s="92">
       <c r="A33" s="93" t="n"/>
+      <c r="B33" s="190" t="n"/>
+      <c r="C33" s="191" t="n"/>
+      <c r="D33" s="191" t="n"/>
+      <c r="E33" s="191" t="n"/>
+      <c r="F33" s="191" t="n"/>
+      <c r="G33" s="191" t="n"/>
+      <c r="H33" s="191" t="n"/>
+      <c r="I33" s="191" t="n"/>
+      <c r="J33" s="192" t="n"/>
       <c r="K33" s="93" t="n"/>
       <c r="L33" s="93" t="n"/>
       <c r="M33" s="93" t="n"/>
@@ -2739,11 +2856,19 @@
     </row>
     <row r="34" ht="27" customHeight="1" s="92">
       <c r="A34" s="93" t="n"/>
-      <c r="B34" s="178" t="inlineStr">
+      <c r="B34" s="193" t="inlineStr">
         <is>
           <t>【振込金額照合（税抜⇔税込の二重計算）】</t>
         </is>
       </c>
+      <c r="C34" s="191" t="n"/>
+      <c r="D34" s="191" t="n"/>
+      <c r="E34" s="191" t="n"/>
+      <c r="F34" s="191" t="n"/>
+      <c r="G34" s="191" t="n"/>
+      <c r="H34" s="191" t="n"/>
+      <c r="I34" s="191" t="n"/>
+      <c r="J34" s="192" t="n"/>
       <c r="K34" s="93" t="n"/>
       <c r="L34" s="93" t="n"/>
       <c r="M34" s="93" t="n"/>
@@ -2763,12 +2888,19 @@
     </row>
     <row r="35" ht="27" customHeight="1" s="92">
       <c r="A35" s="93" t="n"/>
-      <c r="B35" s="183" t="inlineStr">
+      <c r="B35" s="194" t="inlineStr">
         <is>
           <t>① 振込金額（税込・実際に振り込まれた額）</t>
         </is>
       </c>
-      <c r="D35" s="184" t="n"/>
+      <c r="C35" s="195" t="n"/>
+      <c r="D35" s="196" t="n"/>
+      <c r="E35" s="195" t="n"/>
+      <c r="F35" s="195" t="n"/>
+      <c r="G35" s="195" t="n"/>
+      <c r="H35" s="195" t="n"/>
+      <c r="I35" s="195" t="n"/>
+      <c r="J35" s="197" t="n"/>
       <c r="K35" s="93" t="n"/>
       <c r="L35" s="93" t="n"/>
       <c r="M35" s="93" t="n"/>

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -318,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -688,58 +688,80 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium"/>
+      <left style="medium">
+        <color rgb="FFC00000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC00000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC00000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFC00000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
       <right/>
-      <top style="medium"/>
+      <top style="medium">
+        <color rgb="FFC00000"/>
+      </top>
       <bottom/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium"/>
+      <right style="medium">
+        <color rgb="FFC00000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC00000"/>
+      </top>
       <bottom/>
     </border>
     <border>
-      <left/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
+      <left style="medium">
+        <color rgb="FFC00000"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
     </border>
     <border>
       <left/>
-      <right/>
+      <right style="medium">
+        <color rgb="FFC00000"/>
+      </right>
       <top/>
       <bottom/>
     </border>
     <border>
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <left style="medium"/>
+      <left style="medium">
+        <color rgb="FFC00000"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFC00000"/>
+      </bottom>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFC00000"/>
+      </bottom>
     </border>
     <border>
       <left/>
-      <right style="medium"/>
+      <right style="medium">
+        <color rgb="FFC00000"/>
+      </right>
       <top/>
-      <bottom style="medium"/>
+      <bottom style="medium">
+        <color rgb="FFC00000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="6">
@@ -752,7 +774,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="197">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1313,18 +1335,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="32" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="32" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2729,14 +2750,7 @@
     <row r="30" ht="27" customHeight="1" s="92">
       <c r="A30" s="93" t="n"/>
       <c r="B30" s="190" t="n"/>
-      <c r="C30" s="191" t="n"/>
-      <c r="D30" s="191" t="n"/>
-      <c r="E30" s="191" t="n"/>
-      <c r="F30" s="191" t="n"/>
-      <c r="G30" s="191" t="n"/>
-      <c r="H30" s="191" t="n"/>
-      <c r="I30" s="191" t="n"/>
-      <c r="J30" s="192" t="n"/>
+      <c r="J30" s="191" t="n"/>
       <c r="K30" s="175" t="inlineStr">
         <is>
           <t>熱田</t>
@@ -2764,14 +2778,7 @@
     <row r="31" ht="27" customHeight="1" s="92">
       <c r="A31" s="93" t="n"/>
       <c r="B31" s="190" t="n"/>
-      <c r="C31" s="191" t="n"/>
-      <c r="D31" s="191" t="n"/>
-      <c r="E31" s="191" t="n"/>
-      <c r="F31" s="191" t="n"/>
-      <c r="G31" s="191" t="n"/>
-      <c r="H31" s="191" t="n"/>
-      <c r="I31" s="191" t="n"/>
-      <c r="J31" s="192" t="n"/>
+      <c r="J31" s="191" t="n"/>
       <c r="K31" s="176" t="inlineStr">
         <is>
           <t>安保</t>
@@ -2799,14 +2806,7 @@
     <row r="32" ht="27" customHeight="1" s="92">
       <c r="A32" s="93" t="n"/>
       <c r="B32" s="190" t="n"/>
-      <c r="C32" s="191" t="n"/>
-      <c r="D32" s="191" t="n"/>
-      <c r="E32" s="191" t="n"/>
-      <c r="F32" s="191" t="n"/>
-      <c r="G32" s="191" t="n"/>
-      <c r="H32" s="191" t="n"/>
-      <c r="I32" s="191" t="n"/>
-      <c r="J32" s="192" t="n"/>
+      <c r="J32" s="191" t="n"/>
       <c r="K32" s="177" t="n">
         <v>0</v>
       </c>
@@ -2829,14 +2829,7 @@
     <row r="33" ht="27" customHeight="1" s="92">
       <c r="A33" s="93" t="n"/>
       <c r="B33" s="190" t="n"/>
-      <c r="C33" s="191" t="n"/>
-      <c r="D33" s="191" t="n"/>
-      <c r="E33" s="191" t="n"/>
-      <c r="F33" s="191" t="n"/>
-      <c r="G33" s="191" t="n"/>
-      <c r="H33" s="191" t="n"/>
-      <c r="I33" s="191" t="n"/>
-      <c r="J33" s="192" t="n"/>
+      <c r="J33" s="191" t="n"/>
       <c r="K33" s="93" t="n"/>
       <c r="L33" s="93" t="n"/>
       <c r="M33" s="93" t="n"/>
@@ -2856,19 +2849,12 @@
     </row>
     <row r="34" ht="27" customHeight="1" s="92">
       <c r="A34" s="93" t="n"/>
-      <c r="B34" s="193" t="inlineStr">
+      <c r="B34" s="192" t="inlineStr">
         <is>
           <t>【振込金額照合（税抜⇔税込の二重計算）】</t>
         </is>
       </c>
-      <c r="C34" s="191" t="n"/>
-      <c r="D34" s="191" t="n"/>
-      <c r="E34" s="191" t="n"/>
-      <c r="F34" s="191" t="n"/>
-      <c r="G34" s="191" t="n"/>
-      <c r="H34" s="191" t="n"/>
-      <c r="I34" s="191" t="n"/>
-      <c r="J34" s="192" t="n"/>
+      <c r="J34" s="191" t="n"/>
       <c r="K34" s="93" t="n"/>
       <c r="L34" s="93" t="n"/>
       <c r="M34" s="93" t="n"/>
@@ -2888,19 +2874,19 @@
     </row>
     <row r="35" ht="27" customHeight="1" s="92">
       <c r="A35" s="93" t="n"/>
-      <c r="B35" s="194" t="inlineStr">
+      <c r="B35" s="193" t="inlineStr">
         <is>
           <t>① 振込金額（税込・実際に振り込まれた額）</t>
         </is>
       </c>
-      <c r="C35" s="195" t="n"/>
-      <c r="D35" s="196" t="n"/>
-      <c r="E35" s="195" t="n"/>
-      <c r="F35" s="195" t="n"/>
-      <c r="G35" s="195" t="n"/>
-      <c r="H35" s="195" t="n"/>
-      <c r="I35" s="195" t="n"/>
-      <c r="J35" s="197" t="n"/>
+      <c r="C35" s="194" t="n"/>
+      <c r="D35" s="195" t="n"/>
+      <c r="E35" s="194" t="n"/>
+      <c r="F35" s="194" t="n"/>
+      <c r="G35" s="194" t="n"/>
+      <c r="H35" s="194" t="n"/>
+      <c r="I35" s="194" t="n"/>
+      <c r="J35" s="196" t="n"/>
       <c r="K35" s="93" t="n"/>
       <c r="L35" s="93" t="n"/>
       <c r="M35" s="93" t="n"/>
@@ -29976,10 +29962,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -16,14 +16,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="165" formatCode="#,##0_);[RED]\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="&quot;生産課 支払 &quot;#,##0"/>
     <numFmt numFmtId="167" formatCode="&quot;太陽光&quot;0\件"/>
     <numFmt numFmtId="168" formatCode="#,##0;[RED]\▲#,##0"/>
+    <numFmt numFmtId="169" formatCode="#,##0;[Red]▲#,##0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="37">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -266,6 +267,16 @@
       <name val="Meiryo"/>
       <b val="1"/>
       <sz val="17"/>
+    </font>
+    <font>
+      <name val="Noto Sans CJK SC"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -774,7 +785,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="197">
+  <cellXfs count="202">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1346,6 +1357,21 @@
       <alignment horizontal="general" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="34" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1355,7 +1381,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1374,6 +1400,22 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFF9E6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFCCCC"/>
+          <bgColor rgb="00FFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D5F5E3"/>
+          <bgColor rgb="00D5F5E3"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2849,11 +2891,7 @@
     </row>
     <row r="34" ht="27" customHeight="1" s="92">
       <c r="A34" s="93" t="n"/>
-      <c r="B34" s="192" t="inlineStr">
-        <is>
-          <t>【振込金額照合（税抜⇔税込の二重計算）】</t>
-        </is>
-      </c>
+      <c r="B34" s="192" t="n"/>
       <c r="J34" s="191" t="n"/>
       <c r="K34" s="93" t="n"/>
       <c r="L34" s="93" t="n"/>
@@ -2874,11 +2912,7 @@
     </row>
     <row r="35" ht="27" customHeight="1" s="92">
       <c r="A35" s="93" t="n"/>
-      <c r="B35" s="193" t="inlineStr">
-        <is>
-          <t>① 振込金額（税込・実際に振り込まれた額）</t>
-        </is>
-      </c>
+      <c r="B35" s="193" t="n"/>
       <c r="C35" s="194" t="n"/>
       <c r="D35" s="195" t="n"/>
       <c r="E35" s="194" t="n"/>
@@ -2906,11 +2940,7 @@
     </row>
     <row r="36" ht="27" customHeight="1" s="92">
       <c r="A36" s="93" t="n"/>
-      <c r="B36" s="170" t="inlineStr">
-        <is>
-          <t>② 税込相殺（PDF・手入力）</t>
-        </is>
-      </c>
+      <c r="B36" s="170" t="n"/>
       <c r="C36" s="93" t="n"/>
       <c r="D36" s="181" t="n"/>
       <c r="E36" s="93" t="n"/>
@@ -2938,16 +2968,13 @@
     </row>
     <row r="37" ht="27" customHeight="1" s="92">
       <c r="A37" s="93" t="n"/>
-      <c r="B37" s="170" t="inlineStr">
+      <c r="B37" s="197" t="inlineStr">
         <is>
-          <t>③ 税込工事代計（① − ②）</t>
+          <t>【振込金額照合（税抜⇔税込の二重計算）】</t>
         </is>
       </c>
       <c r="C37" s="93" t="n"/>
-      <c r="D37" s="181">
-        <f>D35-D36</f>
-        <v/>
-      </c>
+      <c r="D37" s="181" t="n"/>
       <c r="E37" s="93" t="n"/>
       <c r="F37" s="93" t="n"/>
       <c r="G37" s="93" t="n"/>
@@ -2975,14 +3002,11 @@
       <c r="A38" s="93" t="n"/>
       <c r="B38" s="170" t="inlineStr">
         <is>
-          <t>④ 税抜逆算（③ ÷ 1.1）</t>
+          <t>① 振込金額(税込・実際に振り込まれた額)</t>
         </is>
       </c>
       <c r="C38" s="93" t="n"/>
-      <c r="D38" s="181">
-        <f>ROUND(D37/1.1,0)</f>
-        <v/>
-      </c>
+      <c r="D38" s="198" t="n"/>
       <c r="E38" s="93" t="n"/>
       <c r="F38" s="93" t="n"/>
       <c r="G38" s="93" t="n"/>
@@ -3010,14 +3034,11 @@
       <c r="A39" s="93" t="n"/>
       <c r="B39" s="170" t="inlineStr">
         <is>
-          <t>⑤ Excel税抜合計（J24）</t>
+          <t>② 税込相殺(PDF・手入力)</t>
         </is>
       </c>
       <c r="C39" s="93" t="n"/>
-      <c r="D39" s="181">
-        <f>J24</f>
-        <v/>
-      </c>
+      <c r="D39" s="198" t="n"/>
       <c r="E39" s="93" t="n"/>
       <c r="F39" s="93" t="n"/>
       <c r="G39" s="93" t="n"/>
@@ -3045,12 +3066,12 @@
       <c r="A40" s="93" t="n"/>
       <c r="B40" s="185" t="inlineStr">
         <is>
-          <t>⑥ 差額（⑤ − ④）</t>
+          <t>③ 税込工事代計(① − ②)</t>
         </is>
       </c>
       <c r="C40" s="93" t="n"/>
-      <c r="D40" s="186">
-        <f>D39-D38</f>
+      <c r="D40" s="199">
+        <f>D38-D39</f>
         <v/>
       </c>
       <c r="E40" s="93" t="n"/>
@@ -3080,11 +3101,14 @@
       <c r="A41" s="93" t="n"/>
       <c r="B41" s="93" t="inlineStr">
         <is>
-          <t>※ ±数円→インボイス端数差(正常) / 大きな差→PDF読取エラーの可能性</t>
+          <t>④ 税抜逆算(③ ÷ 1.1)</t>
         </is>
       </c>
       <c r="C41" s="93" t="n"/>
-      <c r="D41" s="93" t="n"/>
+      <c r="D41" s="198">
+        <f>ROUND(D40/1.1,0)</f>
+        <v/>
+      </c>
       <c r="E41" s="93" t="n"/>
       <c r="F41" s="93" t="n"/>
       <c r="G41" s="93" t="n"/>
@@ -3110,9 +3134,16 @@
     </row>
     <row r="42" ht="27" customHeight="1" s="92">
       <c r="A42" s="93" t="n"/>
-      <c r="B42" s="93" t="n"/>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>⑤ Excel税抜合計(J24)</t>
+        </is>
+      </c>
       <c r="C42" s="93" t="n"/>
-      <c r="D42" s="93" t="n"/>
+      <c r="D42" s="198">
+        <f>J24</f>
+        <v/>
+      </c>
       <c r="E42" s="93" t="n"/>
       <c r="F42" s="93" t="n"/>
       <c r="G42" s="93" t="n"/>
@@ -3138,9 +3169,16 @@
     </row>
     <row r="43" ht="27" customHeight="1" s="92">
       <c r="A43" s="93" t="n"/>
-      <c r="B43" s="93" t="n"/>
+      <c r="B43" s="200" t="inlineStr">
+        <is>
+          <t>⑥ 差額(⑤ − ④)</t>
+        </is>
+      </c>
       <c r="C43" s="93" t="n"/>
-      <c r="D43" s="93" t="n"/>
+      <c r="D43" s="201">
+        <f>D42-D41</f>
+        <v/>
+      </c>
       <c r="E43" s="93" t="n"/>
       <c r="F43" s="93" t="n"/>
       <c r="G43" s="93" t="n"/>
@@ -3166,7 +3204,11 @@
     </row>
     <row r="44" ht="27" customHeight="1" s="92">
       <c r="A44" s="93" t="n"/>
-      <c r="B44" s="93" t="n"/>
+      <c r="B44" s="93" t="inlineStr">
+        <is>
+          <t>※ ±数円→インボイス端数差(正常) / 大きな差→PDF読取エラーの可能性</t>
+        </is>
+      </c>
       <c r="C44" s="93" t="n"/>
       <c r="D44" s="93" t="n"/>
       <c r="E44" s="93" t="n"/>
@@ -29962,10 +30004,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
@@ -29985,6 +30027,14 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D43">
+    <cfRule type="expression" priority="5" dxfId="3">
+      <formula>ABS(D43)&gt;10</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="4">
+      <formula>AND(ABS(D43)&lt;=10,D43&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="K5:K23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="班長名エラー" error="山本 / 熱田 / 安保 から選んでください" promptTitle="班長選択" prompt="プルダウンから班長を選んでください" type="list" errorStyle="stop" operator="between">
       <formula1>"山本,熱田,安保"</formula1>

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -329,7 +329,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="54">
+  <borders count="55">
     <border>
       <left/>
       <right/>
@@ -774,6 +774,16 @@
         <color rgb="FFC00000"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC00000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFC00000"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -785,7 +795,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="202">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1372,6 +1382,9 @@
     <xf numFmtId="169" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2756,7 +2769,7 @@
     </row>
     <row r="29" ht="27" customHeight="1" s="92">
       <c r="A29" s="93" t="n"/>
-      <c r="B29" s="187" t="n"/>
+      <c r="B29" s="202" t="n"/>
       <c r="C29" s="188" t="n"/>
       <c r="D29" s="188" t="n"/>
       <c r="E29" s="188" t="n"/>
@@ -30004,10 +30017,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -1679,6 +1679,13 @@
   <cols>
     <col width="9.73" customWidth="1" style="91" min="1" max="1"/>
     <col width="22.53" customWidth="1" style="91" min="2" max="12"/>
+    <col width="18" customWidth="1" style="92" min="4" max="4"/>
+    <col width="18" customWidth="1" style="92" min="5" max="5"/>
+    <col width="18" customWidth="1" style="92" min="6" max="6"/>
+    <col width="18" customWidth="1" style="92" min="7" max="7"/>
+    <col width="18" customWidth="1" style="92" min="8" max="8"/>
+    <col width="18" customWidth="1" style="92" min="9" max="9"/>
+    <col width="18" customWidth="1" style="92" min="10" max="10"/>
     <col width="9" customWidth="1" style="91" min="13" max="26"/>
     <col width="14.4" customWidth="1" style="91" min="27" max="16384"/>
   </cols>
@@ -30017,10 +30024,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -1679,14 +1679,16 @@
   <cols>
     <col width="9.73" customWidth="1" style="91" min="1" max="1"/>
     <col width="22.53" customWidth="1" style="91" min="2" max="12"/>
-    <col width="18" customWidth="1" style="92" min="4" max="4"/>
-    <col width="18" customWidth="1" style="92" min="5" max="5"/>
-    <col width="18" customWidth="1" style="92" min="6" max="6"/>
-    <col width="18" customWidth="1" style="92" min="7" max="7"/>
-    <col width="18" customWidth="1" style="92" min="8" max="8"/>
-    <col width="18" customWidth="1" style="92" min="9" max="9"/>
-    <col width="18" customWidth="1" style="92" min="10" max="10"/>
+    <col width="28" customWidth="1" style="92" min="4" max="4"/>
+    <col width="28" customWidth="1" style="92" min="5" max="5"/>
+    <col width="28" customWidth="1" style="92" min="6" max="6"/>
+    <col width="28" customWidth="1" style="92" min="7" max="7"/>
+    <col width="28" customWidth="1" style="92" min="8" max="8"/>
+    <col width="28" customWidth="1" style="92" min="9" max="9"/>
+    <col width="28" customWidth="1" style="92" min="10" max="10"/>
     <col width="9" customWidth="1" style="91" min="13" max="26"/>
+    <col width="14" customWidth="1" style="92" min="14" max="14"/>
+    <col width="10" customWidth="1" style="92" min="15" max="15"/>
     <col width="14.4" customWidth="1" style="91" min="27" max="16384"/>
   </cols>
   <sheetData>
@@ -30024,10 +30026,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -795,7 +795,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="203">
+  <cellXfs count="204">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1385,6 +1385,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="54" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="14" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1394,7 +1397,7 @@
     <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
     <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -1431,6 +1434,27 @@
           <bgColor rgb="00D5F5E3"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF006100"/>
+      </font>
+      <alignment horizontal="left" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFC65911"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF2E75B6"/>
+      </font>
+      <alignment horizontal="right" vertical="center"/>
     </dxf>
   </dxfs>
   <colors>
@@ -1982,7 +2006,7 @@
         <v/>
       </c>
       <c r="K7" s="133" t="n"/>
-      <c r="L7" s="134">
+      <c r="L7" s="127">
         <f>J7/D7</f>
         <v/>
       </c>
@@ -2574,7 +2598,7 @@
       <c r="I23" s="147" t="n"/>
       <c r="J23" s="142" t="n"/>
       <c r="K23" s="148" t="n"/>
-      <c r="L23" s="149" t="n"/>
+      <c r="L23" s="203" t="n"/>
       <c r="M23" s="93" t="n"/>
       <c r="N23" s="93" t="n"/>
       <c r="O23" s="93" t="n"/>
@@ -30026,10 +30050,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
@@ -30042,6 +30066,15 @@
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
       <formula>AND(K5="",B5&lt;&gt;"")</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="equal" dxfId="5">
+      <formula>"山本"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" dxfId="6">
+      <formula>"熱田"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="9" operator="equal" dxfId="7">
+      <formula>"安保"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O8">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -2747,16 +2747,8 @@
       <c r="H27" s="164" t="n"/>
       <c r="I27" s="165" t="n"/>
       <c r="J27" s="166" t="n"/>
-      <c r="K27" s="170" t="inlineStr">
-        <is>
-          <t>差額</t>
-        </is>
-      </c>
-      <c r="L27" s="170" t="inlineStr">
-        <is>
-          <t>※インボイス端数差</t>
-        </is>
-      </c>
+      <c r="K27" s="170" t="n"/>
+      <c r="L27" s="170" t="n"/>
       <c r="M27" s="93" t="n"/>
       <c r="N27" s="93" t="n"/>
       <c r="O27" s="93" t="n"/>
@@ -30050,10 +30042,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="D40">
     <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -30042,19 +30042,11 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D40">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
-      <formula>ABS(D40)&gt;10</formula>
-    </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
-      <formula>AND(ABS(D40)&lt;=10,D40&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
       <formula>AND(K5="",B5&lt;&gt;"")</formula>

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="168" formatCode="#,##0;[RED]\▲#,##0"/>
     <numFmt numFmtId="169" formatCode="#,##0;[Red]▲#,##0"/>
   </numFmts>
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -277,6 +277,11 @@
       <name val="Meiryo"/>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color theme="1"/>
+      <sz val="17"/>
     </font>
   </fonts>
   <fills count="9">
@@ -795,7 +800,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="204">
+  <cellXfs count="206">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1388,6 +1393,12 @@
     <xf numFmtId="10" fontId="14" fillId="5" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1910,8 +1921,8 @@
       <c r="B5" s="118" t="n"/>
       <c r="C5" s="119" t="n"/>
       <c r="D5" s="120" t="n"/>
-      <c r="E5" s="121" t="n"/>
-      <c r="F5" s="122" t="n"/>
+      <c r="E5" s="204" t="n"/>
+      <c r="F5" s="205" t="n"/>
       <c r="G5" s="123" t="n"/>
       <c r="H5" s="124" t="n"/>
       <c r="I5" s="125" t="n"/>
@@ -30042,10 +30053,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -800,7 +800,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="222">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1399,6 +1399,54 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1920,13 +1968,13 @@
       </c>
       <c r="B5" s="118" t="n"/>
       <c r="C5" s="119" t="n"/>
-      <c r="D5" s="120" t="n"/>
-      <c r="E5" s="204" t="n"/>
-      <c r="F5" s="205" t="n"/>
-      <c r="G5" s="123" t="n"/>
-      <c r="H5" s="124" t="n"/>
-      <c r="I5" s="125" t="n"/>
-      <c r="J5" s="120">
+      <c r="D5" s="206" t="n"/>
+      <c r="E5" s="207" t="n"/>
+      <c r="F5" s="208" t="n"/>
+      <c r="G5" s="209" t="n"/>
+      <c r="H5" s="210" t="n"/>
+      <c r="I5" s="211" t="n"/>
+      <c r="J5" s="206">
         <f>ROUNDDOWN(D5-E5-F5-G5-H5-I5,0)</f>
         <v/>
       </c>
@@ -1963,13 +2011,13 @@
       </c>
       <c r="B6" s="118" t="n"/>
       <c r="C6" s="129" t="n"/>
-      <c r="D6" s="120" t="n"/>
-      <c r="E6" s="130" t="n"/>
-      <c r="F6" s="131" t="n"/>
-      <c r="G6" s="123" t="n"/>
-      <c r="H6" s="124" t="n"/>
-      <c r="I6" s="125" t="n"/>
-      <c r="J6" s="120">
+      <c r="D6" s="206" t="n"/>
+      <c r="E6" s="212" t="n"/>
+      <c r="F6" s="213" t="n"/>
+      <c r="G6" s="209" t="n"/>
+      <c r="H6" s="210" t="n"/>
+      <c r="I6" s="211" t="n"/>
+      <c r="J6" s="206">
         <f>ROUNDDOWN(D6-E6-F6-G6-H6-I6,0)</f>
         <v/>
       </c>
@@ -2006,13 +2054,13 @@
       </c>
       <c r="B7" s="132" t="n"/>
       <c r="C7" s="129" t="n"/>
-      <c r="D7" s="120" t="n"/>
-      <c r="E7" s="130" t="n"/>
-      <c r="F7" s="131" t="n"/>
-      <c r="G7" s="123" t="n"/>
-      <c r="H7" s="124" t="n"/>
-      <c r="I7" s="125" t="n"/>
-      <c r="J7" s="120">
+      <c r="D7" s="206" t="n"/>
+      <c r="E7" s="212" t="n"/>
+      <c r="F7" s="213" t="n"/>
+      <c r="G7" s="209" t="n"/>
+      <c r="H7" s="210" t="n"/>
+      <c r="I7" s="211" t="n"/>
+      <c r="J7" s="206">
         <f>ROUNDDOWN(D7-E7-F7-G7-H7-I7,0)</f>
         <v/>
       </c>
@@ -2049,13 +2097,13 @@
       </c>
       <c r="B8" s="132" t="n"/>
       <c r="C8" s="135" t="n"/>
-      <c r="D8" s="120" t="n"/>
-      <c r="E8" s="130" t="n"/>
-      <c r="F8" s="131" t="n"/>
-      <c r="G8" s="123" t="n"/>
-      <c r="H8" s="124" t="n"/>
-      <c r="I8" s="125" t="n"/>
-      <c r="J8" s="120">
+      <c r="D8" s="206" t="n"/>
+      <c r="E8" s="212" t="n"/>
+      <c r="F8" s="213" t="n"/>
+      <c r="G8" s="209" t="n"/>
+      <c r="H8" s="210" t="n"/>
+      <c r="I8" s="211" t="n"/>
+      <c r="J8" s="206">
         <f>ROUNDDOWN(D8-E8-F8-G8-H8-I8,0)</f>
         <v/>
       </c>
@@ -2092,13 +2140,13 @@
       </c>
       <c r="B9" s="132" t="n"/>
       <c r="C9" s="129" t="n"/>
-      <c r="D9" s="120" t="n"/>
-      <c r="E9" s="130" t="n"/>
-      <c r="F9" s="131" t="n"/>
-      <c r="G9" s="123" t="n"/>
-      <c r="H9" s="124" t="n"/>
-      <c r="I9" s="125" t="n"/>
-      <c r="J9" s="120">
+      <c r="D9" s="206" t="n"/>
+      <c r="E9" s="212" t="n"/>
+      <c r="F9" s="213" t="n"/>
+      <c r="G9" s="209" t="n"/>
+      <c r="H9" s="210" t="n"/>
+      <c r="I9" s="211" t="n"/>
+      <c r="J9" s="206">
         <f>ROUNDDOWN(D9-E9-F9-G9-H9-I9,0)</f>
         <v/>
       </c>
@@ -2135,13 +2183,13 @@
       </c>
       <c r="B10" s="132" t="n"/>
       <c r="C10" s="129" t="n"/>
-      <c r="D10" s="120" t="n"/>
-      <c r="E10" s="130" t="n"/>
-      <c r="F10" s="131" t="n"/>
-      <c r="G10" s="123" t="n"/>
-      <c r="H10" s="124" t="n"/>
-      <c r="I10" s="125" t="n"/>
-      <c r="J10" s="120">
+      <c r="D10" s="206" t="n"/>
+      <c r="E10" s="212" t="n"/>
+      <c r="F10" s="213" t="n"/>
+      <c r="G10" s="209" t="n"/>
+      <c r="H10" s="210" t="n"/>
+      <c r="I10" s="211" t="n"/>
+      <c r="J10" s="206">
         <f>ROUNDDOWN(D10-E10-F10-G10-H10-I10,0)</f>
         <v/>
       </c>
@@ -2171,13 +2219,13 @@
       </c>
       <c r="B11" s="132" t="n"/>
       <c r="C11" s="129" t="n"/>
-      <c r="D11" s="120" t="n"/>
-      <c r="E11" s="130" t="n"/>
-      <c r="F11" s="131" t="n"/>
-      <c r="G11" s="123" t="n"/>
-      <c r="H11" s="124" t="n"/>
-      <c r="I11" s="125" t="n"/>
-      <c r="J11" s="120">
+      <c r="D11" s="206" t="n"/>
+      <c r="E11" s="212" t="n"/>
+      <c r="F11" s="213" t="n"/>
+      <c r="G11" s="209" t="n"/>
+      <c r="H11" s="210" t="n"/>
+      <c r="I11" s="211" t="n"/>
+      <c r="J11" s="206">
         <f>ROUNDDOWN(D11-E11-F11-G11-H11-I11,0)</f>
         <v/>
       </c>
@@ -2207,13 +2255,13 @@
       </c>
       <c r="B12" s="132" t="n"/>
       <c r="C12" s="129" t="n"/>
-      <c r="D12" s="120" t="n"/>
-      <c r="E12" s="130" t="n"/>
-      <c r="F12" s="131" t="n"/>
-      <c r="G12" s="123" t="n"/>
-      <c r="H12" s="124" t="n"/>
-      <c r="I12" s="125" t="n"/>
-      <c r="J12" s="120">
+      <c r="D12" s="206" t="n"/>
+      <c r="E12" s="212" t="n"/>
+      <c r="F12" s="213" t="n"/>
+      <c r="G12" s="209" t="n"/>
+      <c r="H12" s="210" t="n"/>
+      <c r="I12" s="211" t="n"/>
+      <c r="J12" s="206">
         <f>ROUNDDOWN(D12-E12-F12-G12-H12-I12,0)</f>
         <v/>
       </c>
@@ -2243,13 +2291,13 @@
       </c>
       <c r="B13" s="132" t="n"/>
       <c r="C13" s="129" t="n"/>
-      <c r="D13" s="120" t="n"/>
-      <c r="E13" s="130" t="n"/>
-      <c r="F13" s="131" t="n"/>
-      <c r="G13" s="123" t="n"/>
-      <c r="H13" s="124" t="n"/>
-      <c r="I13" s="125" t="n"/>
-      <c r="J13" s="120">
+      <c r="D13" s="206" t="n"/>
+      <c r="E13" s="212" t="n"/>
+      <c r="F13" s="213" t="n"/>
+      <c r="G13" s="209" t="n"/>
+      <c r="H13" s="210" t="n"/>
+      <c r="I13" s="211" t="n"/>
+      <c r="J13" s="206">
         <f>ROUNDDOWN(D13-E13-F13-G13-H13-I13,0)</f>
         <v/>
       </c>
@@ -2279,13 +2327,13 @@
       </c>
       <c r="B14" s="132" t="n"/>
       <c r="C14" s="129" t="n"/>
-      <c r="D14" s="120" t="n"/>
-      <c r="E14" s="130" t="n"/>
-      <c r="F14" s="131" t="n"/>
-      <c r="G14" s="123" t="n"/>
-      <c r="H14" s="124" t="n"/>
-      <c r="I14" s="125" t="n"/>
-      <c r="J14" s="120">
+      <c r="D14" s="206" t="n"/>
+      <c r="E14" s="212" t="n"/>
+      <c r="F14" s="213" t="n"/>
+      <c r="G14" s="209" t="n"/>
+      <c r="H14" s="210" t="n"/>
+      <c r="I14" s="211" t="n"/>
+      <c r="J14" s="206">
         <f>ROUNDDOWN(D14-E14-F14-G14-H14-I14,0)</f>
         <v/>
       </c>
@@ -2315,13 +2363,13 @@
       </c>
       <c r="B15" s="132" t="n"/>
       <c r="C15" s="129" t="n"/>
-      <c r="D15" s="120" t="n"/>
-      <c r="E15" s="130" t="n"/>
-      <c r="F15" s="131" t="n"/>
-      <c r="G15" s="123" t="n"/>
-      <c r="H15" s="124" t="n"/>
-      <c r="I15" s="125" t="n"/>
-      <c r="J15" s="120">
+      <c r="D15" s="206" t="n"/>
+      <c r="E15" s="212" t="n"/>
+      <c r="F15" s="213" t="n"/>
+      <c r="G15" s="209" t="n"/>
+      <c r="H15" s="210" t="n"/>
+      <c r="I15" s="211" t="n"/>
+      <c r="J15" s="206">
         <f>ROUNDDOWN(D15-E15-F15-G15-H15-I15,0)</f>
         <v/>
       </c>
@@ -2351,13 +2399,13 @@
       </c>
       <c r="B16" s="132" t="n"/>
       <c r="C16" s="129" t="n"/>
-      <c r="D16" s="120" t="n"/>
-      <c r="E16" s="130" t="n"/>
-      <c r="F16" s="131" t="n"/>
-      <c r="G16" s="123" t="n"/>
-      <c r="H16" s="124" t="n"/>
-      <c r="I16" s="125" t="n"/>
-      <c r="J16" s="120">
+      <c r="D16" s="206" t="n"/>
+      <c r="E16" s="212" t="n"/>
+      <c r="F16" s="213" t="n"/>
+      <c r="G16" s="209" t="n"/>
+      <c r="H16" s="210" t="n"/>
+      <c r="I16" s="211" t="n"/>
+      <c r="J16" s="206">
         <f>ROUNDDOWN(D16-E16-F16-G16-H16-I16,0)</f>
         <v/>
       </c>
@@ -2387,13 +2435,13 @@
       </c>
       <c r="B17" s="132" t="n"/>
       <c r="C17" s="129" t="n"/>
-      <c r="D17" s="120" t="n"/>
-      <c r="E17" s="130" t="n"/>
-      <c r="F17" s="131" t="n"/>
-      <c r="G17" s="123" t="n"/>
-      <c r="H17" s="124" t="n"/>
-      <c r="I17" s="125" t="n"/>
-      <c r="J17" s="120">
+      <c r="D17" s="206" t="n"/>
+      <c r="E17" s="212" t="n"/>
+      <c r="F17" s="213" t="n"/>
+      <c r="G17" s="209" t="n"/>
+      <c r="H17" s="210" t="n"/>
+      <c r="I17" s="211" t="n"/>
+      <c r="J17" s="206">
         <f>ROUNDDOWN(D17-E17-F17-G17-H17-I17,0)</f>
         <v/>
       </c>
@@ -2423,13 +2471,13 @@
       </c>
       <c r="B18" s="132" t="n"/>
       <c r="C18" s="129" t="n"/>
-      <c r="D18" s="120" t="n"/>
-      <c r="E18" s="130" t="n"/>
-      <c r="F18" s="131" t="n"/>
-      <c r="G18" s="123" t="n"/>
-      <c r="H18" s="124" t="n"/>
-      <c r="I18" s="125" t="n"/>
-      <c r="J18" s="120">
+      <c r="D18" s="206" t="n"/>
+      <c r="E18" s="212" t="n"/>
+      <c r="F18" s="213" t="n"/>
+      <c r="G18" s="209" t="n"/>
+      <c r="H18" s="210" t="n"/>
+      <c r="I18" s="211" t="n"/>
+      <c r="J18" s="206">
         <f>ROUNDDOWN(D18-E18-F18-G18-H18-I18,0)</f>
         <v/>
       </c>
@@ -2459,13 +2507,13 @@
       </c>
       <c r="B19" s="132" t="n"/>
       <c r="C19" s="129" t="n"/>
-      <c r="D19" s="120" t="n"/>
-      <c r="E19" s="130" t="n"/>
-      <c r="F19" s="131" t="n"/>
-      <c r="G19" s="123" t="n"/>
-      <c r="H19" s="124" t="n"/>
-      <c r="I19" s="125" t="n"/>
-      <c r="J19" s="120">
+      <c r="D19" s="206" t="n"/>
+      <c r="E19" s="212" t="n"/>
+      <c r="F19" s="213" t="n"/>
+      <c r="G19" s="209" t="n"/>
+      <c r="H19" s="210" t="n"/>
+      <c r="I19" s="211" t="n"/>
+      <c r="J19" s="206">
         <f>ROUNDDOWN(D19-E19-F19-G19-H19-I19,0)</f>
         <v/>
       </c>
@@ -2495,13 +2543,13 @@
       </c>
       <c r="B20" s="132" t="n"/>
       <c r="C20" s="129" t="n"/>
-      <c r="D20" s="120" t="n"/>
-      <c r="E20" s="130" t="n"/>
-      <c r="F20" s="131" t="n"/>
-      <c r="G20" s="123" t="n"/>
-      <c r="H20" s="124" t="n"/>
-      <c r="I20" s="125" t="n"/>
-      <c r="J20" s="120">
+      <c r="D20" s="206" t="n"/>
+      <c r="E20" s="212" t="n"/>
+      <c r="F20" s="213" t="n"/>
+      <c r="G20" s="209" t="n"/>
+      <c r="H20" s="210" t="n"/>
+      <c r="I20" s="211" t="n"/>
+      <c r="J20" s="206">
         <f>ROUNDDOWN(D20-E20-F20-G20-H20-I20,0)</f>
         <v/>
       </c>
@@ -2531,13 +2579,13 @@
       </c>
       <c r="B21" s="132" t="n"/>
       <c r="C21" s="129" t="n"/>
-      <c r="D21" s="120" t="n"/>
-      <c r="E21" s="130" t="n"/>
-      <c r="F21" s="131" t="n"/>
-      <c r="G21" s="123" t="n"/>
-      <c r="H21" s="124" t="n"/>
-      <c r="I21" s="125" t="n"/>
-      <c r="J21" s="120">
+      <c r="D21" s="206" t="n"/>
+      <c r="E21" s="212" t="n"/>
+      <c r="F21" s="213" t="n"/>
+      <c r="G21" s="209" t="n"/>
+      <c r="H21" s="210" t="n"/>
+      <c r="I21" s="211" t="n"/>
+      <c r="J21" s="206">
         <f>ROUNDDOWN(D21-E21-F21-G21-H21-I21,0)</f>
         <v/>
       </c>
@@ -2567,13 +2615,13 @@
       </c>
       <c r="B22" s="132" t="n"/>
       <c r="C22" s="129" t="n"/>
-      <c r="D22" s="120" t="n"/>
-      <c r="E22" s="130" t="n"/>
-      <c r="F22" s="131" t="n"/>
-      <c r="G22" s="123" t="n"/>
-      <c r="H22" s="124" t="n"/>
-      <c r="I22" s="125" t="n"/>
-      <c r="J22" s="120">
+      <c r="D22" s="206" t="n"/>
+      <c r="E22" s="212" t="n"/>
+      <c r="F22" s="213" t="n"/>
+      <c r="G22" s="209" t="n"/>
+      <c r="H22" s="210" t="n"/>
+      <c r="I22" s="211" t="n"/>
+      <c r="J22" s="206">
         <f>ROUNDDOWN(D22-E22-F22-G22-H22-I22,0)</f>
         <v/>
       </c>
@@ -2601,13 +2649,13 @@
       <c r="A23" s="93" t="n"/>
       <c r="B23" s="140" t="n"/>
       <c r="C23" s="141" t="n"/>
-      <c r="D23" s="142" t="n"/>
-      <c r="E23" s="143" t="n"/>
-      <c r="F23" s="144" t="n"/>
-      <c r="G23" s="145" t="n"/>
-      <c r="H23" s="146" t="n"/>
-      <c r="I23" s="147" t="n"/>
-      <c r="J23" s="142" t="n"/>
+      <c r="D23" s="214" t="n"/>
+      <c r="E23" s="215" t="n"/>
+      <c r="F23" s="216" t="n"/>
+      <c r="G23" s="217" t="n"/>
+      <c r="H23" s="218" t="n"/>
+      <c r="I23" s="219" t="n"/>
+      <c r="J23" s="214" t="n"/>
       <c r="K23" s="148" t="n"/>
       <c r="L23" s="203" t="n"/>
       <c r="M23" s="93" t="n"/>
@@ -2721,7 +2769,7 @@
       <c r="B26" s="93" t="n"/>
       <c r="C26" s="161" t="n"/>
       <c r="D26" s="161" t="n"/>
-      <c r="E26" s="162">
+      <c r="E26" s="220">
         <f>SUM(E24:F24)</f>
         <v/>
       </c>
@@ -3113,13 +3161,13 @@
     </row>
     <row r="40" ht="27" customHeight="1" s="92">
       <c r="A40" s="93" t="n"/>
-      <c r="B40" s="185" t="inlineStr">
+      <c r="B40" s="183" t="inlineStr">
         <is>
           <t>③ 税込工事代計(① − ②)</t>
         </is>
       </c>
       <c r="C40" s="93" t="n"/>
-      <c r="D40" s="199">
+      <c r="D40" s="221">
         <f>D38-D39</f>
         <v/>
       </c>
@@ -30053,10 +30101,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -800,7 +800,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="222">
+  <cellXfs count="224">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1447,6 +1447,12 @@
     <xf numFmtId="169" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1968,13 +1974,13 @@
       </c>
       <c r="B5" s="118" t="n"/>
       <c r="C5" s="119" t="n"/>
-      <c r="D5" s="206" t="n"/>
-      <c r="E5" s="207" t="n"/>
-      <c r="F5" s="208" t="n"/>
-      <c r="G5" s="209" t="n"/>
-      <c r="H5" s="210" t="n"/>
-      <c r="I5" s="211" t="n"/>
-      <c r="J5" s="206">
+      <c r="D5" s="120" t="n"/>
+      <c r="E5" s="222" t="n"/>
+      <c r="F5" s="223" t="n"/>
+      <c r="G5" s="123" t="n"/>
+      <c r="H5" s="124" t="n"/>
+      <c r="I5" s="125" t="n"/>
+      <c r="J5" s="120">
         <f>ROUNDDOWN(D5-E5-F5-G5-H5-I5,0)</f>
         <v/>
       </c>
@@ -2011,13 +2017,13 @@
       </c>
       <c r="B6" s="118" t="n"/>
       <c r="C6" s="129" t="n"/>
-      <c r="D6" s="206" t="n"/>
-      <c r="E6" s="212" t="n"/>
-      <c r="F6" s="213" t="n"/>
-      <c r="G6" s="209" t="n"/>
-      <c r="H6" s="210" t="n"/>
-      <c r="I6" s="211" t="n"/>
-      <c r="J6" s="206">
+      <c r="D6" s="120" t="n"/>
+      <c r="E6" s="130" t="n"/>
+      <c r="F6" s="131" t="n"/>
+      <c r="G6" s="123" t="n"/>
+      <c r="H6" s="124" t="n"/>
+      <c r="I6" s="125" t="n"/>
+      <c r="J6" s="120">
         <f>ROUNDDOWN(D6-E6-F6-G6-H6-I6,0)</f>
         <v/>
       </c>
@@ -2054,13 +2060,13 @@
       </c>
       <c r="B7" s="132" t="n"/>
       <c r="C7" s="129" t="n"/>
-      <c r="D7" s="206" t="n"/>
-      <c r="E7" s="212" t="n"/>
-      <c r="F7" s="213" t="n"/>
-      <c r="G7" s="209" t="n"/>
-      <c r="H7" s="210" t="n"/>
-      <c r="I7" s="211" t="n"/>
-      <c r="J7" s="206">
+      <c r="D7" s="120" t="n"/>
+      <c r="E7" s="130" t="n"/>
+      <c r="F7" s="131" t="n"/>
+      <c r="G7" s="123" t="n"/>
+      <c r="H7" s="124" t="n"/>
+      <c r="I7" s="125" t="n"/>
+      <c r="J7" s="120">
         <f>ROUNDDOWN(D7-E7-F7-G7-H7-I7,0)</f>
         <v/>
       </c>
@@ -2097,13 +2103,13 @@
       </c>
       <c r="B8" s="132" t="n"/>
       <c r="C8" s="135" t="n"/>
-      <c r="D8" s="206" t="n"/>
-      <c r="E8" s="212" t="n"/>
-      <c r="F8" s="213" t="n"/>
-      <c r="G8" s="209" t="n"/>
-      <c r="H8" s="210" t="n"/>
-      <c r="I8" s="211" t="n"/>
-      <c r="J8" s="206">
+      <c r="D8" s="120" t="n"/>
+      <c r="E8" s="130" t="n"/>
+      <c r="F8" s="131" t="n"/>
+      <c r="G8" s="123" t="n"/>
+      <c r="H8" s="124" t="n"/>
+      <c r="I8" s="125" t="n"/>
+      <c r="J8" s="120">
         <f>ROUNDDOWN(D8-E8-F8-G8-H8-I8,0)</f>
         <v/>
       </c>
@@ -2140,13 +2146,13 @@
       </c>
       <c r="B9" s="132" t="n"/>
       <c r="C9" s="129" t="n"/>
-      <c r="D9" s="206" t="n"/>
-      <c r="E9" s="212" t="n"/>
-      <c r="F9" s="213" t="n"/>
-      <c r="G9" s="209" t="n"/>
-      <c r="H9" s="210" t="n"/>
-      <c r="I9" s="211" t="n"/>
-      <c r="J9" s="206">
+      <c r="D9" s="120" t="n"/>
+      <c r="E9" s="130" t="n"/>
+      <c r="F9" s="131" t="n"/>
+      <c r="G9" s="123" t="n"/>
+      <c r="H9" s="124" t="n"/>
+      <c r="I9" s="125" t="n"/>
+      <c r="J9" s="120">
         <f>ROUNDDOWN(D9-E9-F9-G9-H9-I9,0)</f>
         <v/>
       </c>
@@ -2183,13 +2189,13 @@
       </c>
       <c r="B10" s="132" t="n"/>
       <c r="C10" s="129" t="n"/>
-      <c r="D10" s="206" t="n"/>
-      <c r="E10" s="212" t="n"/>
-      <c r="F10" s="213" t="n"/>
-      <c r="G10" s="209" t="n"/>
-      <c r="H10" s="210" t="n"/>
-      <c r="I10" s="211" t="n"/>
-      <c r="J10" s="206">
+      <c r="D10" s="120" t="n"/>
+      <c r="E10" s="130" t="n"/>
+      <c r="F10" s="131" t="n"/>
+      <c r="G10" s="123" t="n"/>
+      <c r="H10" s="124" t="n"/>
+      <c r="I10" s="125" t="n"/>
+      <c r="J10" s="120">
         <f>ROUNDDOWN(D10-E10-F10-G10-H10-I10,0)</f>
         <v/>
       </c>
@@ -2219,13 +2225,13 @@
       </c>
       <c r="B11" s="132" t="n"/>
       <c r="C11" s="129" t="n"/>
-      <c r="D11" s="206" t="n"/>
-      <c r="E11" s="212" t="n"/>
-      <c r="F11" s="213" t="n"/>
-      <c r="G11" s="209" t="n"/>
-      <c r="H11" s="210" t="n"/>
-      <c r="I11" s="211" t="n"/>
-      <c r="J11" s="206">
+      <c r="D11" s="120" t="n"/>
+      <c r="E11" s="130" t="n"/>
+      <c r="F11" s="131" t="n"/>
+      <c r="G11" s="123" t="n"/>
+      <c r="H11" s="124" t="n"/>
+      <c r="I11" s="125" t="n"/>
+      <c r="J11" s="120">
         <f>ROUNDDOWN(D11-E11-F11-G11-H11-I11,0)</f>
         <v/>
       </c>
@@ -2255,13 +2261,13 @@
       </c>
       <c r="B12" s="132" t="n"/>
       <c r="C12" s="129" t="n"/>
-      <c r="D12" s="206" t="n"/>
-      <c r="E12" s="212" t="n"/>
-      <c r="F12" s="213" t="n"/>
-      <c r="G12" s="209" t="n"/>
-      <c r="H12" s="210" t="n"/>
-      <c r="I12" s="211" t="n"/>
-      <c r="J12" s="206">
+      <c r="D12" s="120" t="n"/>
+      <c r="E12" s="130" t="n"/>
+      <c r="F12" s="131" t="n"/>
+      <c r="G12" s="123" t="n"/>
+      <c r="H12" s="124" t="n"/>
+      <c r="I12" s="125" t="n"/>
+      <c r="J12" s="120">
         <f>ROUNDDOWN(D12-E12-F12-G12-H12-I12,0)</f>
         <v/>
       </c>
@@ -2291,13 +2297,13 @@
       </c>
       <c r="B13" s="132" t="n"/>
       <c r="C13" s="129" t="n"/>
-      <c r="D13" s="206" t="n"/>
-      <c r="E13" s="212" t="n"/>
-      <c r="F13" s="213" t="n"/>
-      <c r="G13" s="209" t="n"/>
-      <c r="H13" s="210" t="n"/>
-      <c r="I13" s="211" t="n"/>
-      <c r="J13" s="206">
+      <c r="D13" s="120" t="n"/>
+      <c r="E13" s="130" t="n"/>
+      <c r="F13" s="131" t="n"/>
+      <c r="G13" s="123" t="n"/>
+      <c r="H13" s="124" t="n"/>
+      <c r="I13" s="125" t="n"/>
+      <c r="J13" s="120">
         <f>ROUNDDOWN(D13-E13-F13-G13-H13-I13,0)</f>
         <v/>
       </c>
@@ -2327,13 +2333,13 @@
       </c>
       <c r="B14" s="132" t="n"/>
       <c r="C14" s="129" t="n"/>
-      <c r="D14" s="206" t="n"/>
-      <c r="E14" s="212" t="n"/>
-      <c r="F14" s="213" t="n"/>
-      <c r="G14" s="209" t="n"/>
-      <c r="H14" s="210" t="n"/>
-      <c r="I14" s="211" t="n"/>
-      <c r="J14" s="206">
+      <c r="D14" s="120" t="n"/>
+      <c r="E14" s="130" t="n"/>
+      <c r="F14" s="131" t="n"/>
+      <c r="G14" s="123" t="n"/>
+      <c r="H14" s="124" t="n"/>
+      <c r="I14" s="125" t="n"/>
+      <c r="J14" s="120">
         <f>ROUNDDOWN(D14-E14-F14-G14-H14-I14,0)</f>
         <v/>
       </c>
@@ -2363,13 +2369,13 @@
       </c>
       <c r="B15" s="132" t="n"/>
       <c r="C15" s="129" t="n"/>
-      <c r="D15" s="206" t="n"/>
-      <c r="E15" s="212" t="n"/>
-      <c r="F15" s="213" t="n"/>
-      <c r="G15" s="209" t="n"/>
-      <c r="H15" s="210" t="n"/>
-      <c r="I15" s="211" t="n"/>
-      <c r="J15" s="206">
+      <c r="D15" s="120" t="n"/>
+      <c r="E15" s="130" t="n"/>
+      <c r="F15" s="131" t="n"/>
+      <c r="G15" s="123" t="n"/>
+      <c r="H15" s="124" t="n"/>
+      <c r="I15" s="125" t="n"/>
+      <c r="J15" s="120">
         <f>ROUNDDOWN(D15-E15-F15-G15-H15-I15,0)</f>
         <v/>
       </c>
@@ -2399,13 +2405,13 @@
       </c>
       <c r="B16" s="132" t="n"/>
       <c r="C16" s="129" t="n"/>
-      <c r="D16" s="206" t="n"/>
-      <c r="E16" s="212" t="n"/>
-      <c r="F16" s="213" t="n"/>
-      <c r="G16" s="209" t="n"/>
-      <c r="H16" s="210" t="n"/>
-      <c r="I16" s="211" t="n"/>
-      <c r="J16" s="206">
+      <c r="D16" s="120" t="n"/>
+      <c r="E16" s="130" t="n"/>
+      <c r="F16" s="131" t="n"/>
+      <c r="G16" s="123" t="n"/>
+      <c r="H16" s="124" t="n"/>
+      <c r="I16" s="125" t="n"/>
+      <c r="J16" s="120">
         <f>ROUNDDOWN(D16-E16-F16-G16-H16-I16,0)</f>
         <v/>
       </c>
@@ -2435,13 +2441,13 @@
       </c>
       <c r="B17" s="132" t="n"/>
       <c r="C17" s="129" t="n"/>
-      <c r="D17" s="206" t="n"/>
-      <c r="E17" s="212" t="n"/>
-      <c r="F17" s="213" t="n"/>
-      <c r="G17" s="209" t="n"/>
-      <c r="H17" s="210" t="n"/>
-      <c r="I17" s="211" t="n"/>
-      <c r="J17" s="206">
+      <c r="D17" s="120" t="n"/>
+      <c r="E17" s="130" t="n"/>
+      <c r="F17" s="131" t="n"/>
+      <c r="G17" s="123" t="n"/>
+      <c r="H17" s="124" t="n"/>
+      <c r="I17" s="125" t="n"/>
+      <c r="J17" s="120">
         <f>ROUNDDOWN(D17-E17-F17-G17-H17-I17,0)</f>
         <v/>
       </c>
@@ -2471,13 +2477,13 @@
       </c>
       <c r="B18" s="132" t="n"/>
       <c r="C18" s="129" t="n"/>
-      <c r="D18" s="206" t="n"/>
-      <c r="E18" s="212" t="n"/>
-      <c r="F18" s="213" t="n"/>
-      <c r="G18" s="209" t="n"/>
-      <c r="H18" s="210" t="n"/>
-      <c r="I18" s="211" t="n"/>
-      <c r="J18" s="206">
+      <c r="D18" s="120" t="n"/>
+      <c r="E18" s="130" t="n"/>
+      <c r="F18" s="131" t="n"/>
+      <c r="G18" s="123" t="n"/>
+      <c r="H18" s="124" t="n"/>
+      <c r="I18" s="125" t="n"/>
+      <c r="J18" s="120">
         <f>ROUNDDOWN(D18-E18-F18-G18-H18-I18,0)</f>
         <v/>
       </c>
@@ -2507,13 +2513,13 @@
       </c>
       <c r="B19" s="132" t="n"/>
       <c r="C19" s="129" t="n"/>
-      <c r="D19" s="206" t="n"/>
-      <c r="E19" s="212" t="n"/>
-      <c r="F19" s="213" t="n"/>
-      <c r="G19" s="209" t="n"/>
-      <c r="H19" s="210" t="n"/>
-      <c r="I19" s="211" t="n"/>
-      <c r="J19" s="206">
+      <c r="D19" s="120" t="n"/>
+      <c r="E19" s="130" t="n"/>
+      <c r="F19" s="131" t="n"/>
+      <c r="G19" s="123" t="n"/>
+      <c r="H19" s="124" t="n"/>
+      <c r="I19" s="125" t="n"/>
+      <c r="J19" s="120">
         <f>ROUNDDOWN(D19-E19-F19-G19-H19-I19,0)</f>
         <v/>
       </c>
@@ -2543,13 +2549,13 @@
       </c>
       <c r="B20" s="132" t="n"/>
       <c r="C20" s="129" t="n"/>
-      <c r="D20" s="206" t="n"/>
-      <c r="E20" s="212" t="n"/>
-      <c r="F20" s="213" t="n"/>
-      <c r="G20" s="209" t="n"/>
-      <c r="H20" s="210" t="n"/>
-      <c r="I20" s="211" t="n"/>
-      <c r="J20" s="206">
+      <c r="D20" s="120" t="n"/>
+      <c r="E20" s="130" t="n"/>
+      <c r="F20" s="131" t="n"/>
+      <c r="G20" s="123" t="n"/>
+      <c r="H20" s="124" t="n"/>
+      <c r="I20" s="125" t="n"/>
+      <c r="J20" s="120">
         <f>ROUNDDOWN(D20-E20-F20-G20-H20-I20,0)</f>
         <v/>
       </c>
@@ -2579,13 +2585,13 @@
       </c>
       <c r="B21" s="132" t="n"/>
       <c r="C21" s="129" t="n"/>
-      <c r="D21" s="206" t="n"/>
-      <c r="E21" s="212" t="n"/>
-      <c r="F21" s="213" t="n"/>
-      <c r="G21" s="209" t="n"/>
-      <c r="H21" s="210" t="n"/>
-      <c r="I21" s="211" t="n"/>
-      <c r="J21" s="206">
+      <c r="D21" s="120" t="n"/>
+      <c r="E21" s="130" t="n"/>
+      <c r="F21" s="131" t="n"/>
+      <c r="G21" s="123" t="n"/>
+      <c r="H21" s="124" t="n"/>
+      <c r="I21" s="125" t="n"/>
+      <c r="J21" s="120">
         <f>ROUNDDOWN(D21-E21-F21-G21-H21-I21,0)</f>
         <v/>
       </c>
@@ -2615,13 +2621,13 @@
       </c>
       <c r="B22" s="132" t="n"/>
       <c r="C22" s="129" t="n"/>
-      <c r="D22" s="206" t="n"/>
-      <c r="E22" s="212" t="n"/>
-      <c r="F22" s="213" t="n"/>
-      <c r="G22" s="209" t="n"/>
-      <c r="H22" s="210" t="n"/>
-      <c r="I22" s="211" t="n"/>
-      <c r="J22" s="206">
+      <c r="D22" s="120" t="n"/>
+      <c r="E22" s="130" t="n"/>
+      <c r="F22" s="131" t="n"/>
+      <c r="G22" s="123" t="n"/>
+      <c r="H22" s="124" t="n"/>
+      <c r="I22" s="125" t="n"/>
+      <c r="J22" s="120">
         <f>ROUNDDOWN(D22-E22-F22-G22-H22-I22,0)</f>
         <v/>
       </c>
@@ -2649,13 +2655,13 @@
       <c r="A23" s="93" t="n"/>
       <c r="B23" s="140" t="n"/>
       <c r="C23" s="141" t="n"/>
-      <c r="D23" s="214" t="n"/>
-      <c r="E23" s="215" t="n"/>
-      <c r="F23" s="216" t="n"/>
-      <c r="G23" s="217" t="n"/>
-      <c r="H23" s="218" t="n"/>
-      <c r="I23" s="219" t="n"/>
-      <c r="J23" s="214" t="n"/>
+      <c r="D23" s="142" t="n"/>
+      <c r="E23" s="143" t="n"/>
+      <c r="F23" s="144" t="n"/>
+      <c r="G23" s="145" t="n"/>
+      <c r="H23" s="146" t="n"/>
+      <c r="I23" s="147" t="n"/>
+      <c r="J23" s="142" t="n"/>
       <c r="K23" s="148" t="n"/>
       <c r="L23" s="203" t="n"/>
       <c r="M23" s="93" t="n"/>
@@ -30101,10 +30107,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="E26:F27"/>
     <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="K1:L1"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="E26:F27"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -800,7 +800,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="224">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1453,6 +1453,12 @@
     <xf numFmtId="0" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1975,8 +1981,8 @@
       <c r="B5" s="118" t="n"/>
       <c r="C5" s="119" t="n"/>
       <c r="D5" s="120" t="n"/>
-      <c r="E5" s="222" t="n"/>
-      <c r="F5" s="223" t="n"/>
+      <c r="E5" s="224" t="n"/>
+      <c r="F5" s="225" t="n"/>
       <c r="G5" s="123" t="n"/>
       <c r="H5" s="124" t="n"/>
       <c r="I5" s="125" t="n"/>
@@ -30107,10 +30113,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="E25:H25"/>
     <mergeCell ref="E26:F27"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:H25"/>
-    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K23">
     <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">

--- a/template/集計用.xlsx
+++ b/template/集計用.xlsx
@@ -334,7 +334,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="55">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -789,6 +789,20 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -800,7 +814,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="226">
+  <cellXfs count="229">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1459,6 +1473,15 @@
     <xf numFmtId="165" fontId="37" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1978,7 +2001,7 @@
       <c r="A5" s="93" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="118" t="n"/>
+      <c r="B5" s="226" t="n"/>
       <c r="C5" s="119" t="n"/>
       <c r="D5" s="120" t="n"/>
       <c r="E5" s="224" t="n"/>
@@ -2021,7 +2044,7 @@
       <c r="A6" s="93" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="118" t="n"/>
+      <c r="B6" s="226" t="n"/>
       <c r="C6" s="129" t="n"/>
       <c r="D6" s="120" t="n"/>
       <c r="E6" s="130" t="n"/>
@@ -2064,7 +2087,7 @@
       <c r="A7" s="93" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="132" t="n"/>
+      <c r="B7" s="227" t="n"/>
       <c r="C7" s="129" t="n"/>
       <c r="D7" s="120" t="n"/>
       <c r="E7" s="130" t="n"/>
@@ -2107,7 +2130,7 @@
       <c r="A8" s="93" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="132" t="n"/>
+      <c r="B8" s="227" t="n"/>
       <c r="C8" s="135" t="n"/>
       <c r="D8" s="120" t="n"/>
       <c r="E8" s="130" t="n"/>
@@ -2150,7 +2173,7 @@
       <c r="A9" s="93" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="132" t="n"/>
+      <c r="B9" s="227" t="n"/>
       <c r="C9" s="129" t="n"/>
       <c r="D9" s="120" t="n"/>
       <c r="E9" s="130" t="n"/>
@@ -2193,7 +2216,7 @@
       <c r="A10" s="93" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="132" t="n"/>
+      <c r="B10" s="227" t="n"/>
       <c r="C10" s="129" t="n"/>
       <c r="D10" s="120" t="n"/>
       <c r="E10" s="130" t="n"/>
@@ -2229,7 +2252,7 @@
       <c r="A11" s="93" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="132" t="n"/>
+      <c r="B11" s="227" t="n"/>
       <c r="C11" s="129" t="n"/>
       <c r="D11" s="120" t="n"/>
       <c r="E11" s="130" t="n"/>
@@ -2265,7 +2288,7 @@
       <c r="A12" s="93" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="132" t="n"/>
+      <c r="B12" s="227" t="n"/>
       <c r="C12" s="129" t="n"/>
       <c r="D12" s="120" t="n"/>
       <c r="E12" s="130" t="n"/>
@@ -2301,7 +2324,7 @@
       <c r="A13" s="93" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="132" t="n"/>
+      <c r="B13" s="227" t="n"/>
       <c r="C13" s="129" t="n"/>
       <c r="D13" s="120" t="n"/>
       <c r="E13" s="130" t="n"/>
@@ -2337,7 +2360,7 @@
       <c r="A14" s="93" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="132" t="n"/>
+      <c r="B14" s="227" t="n"/>
       <c r="C14" s="129" t="n"/>
       <c r="D14" s="120" t="n"/>
       <c r="E14" s="130" t="n"/>
@@ -2373,7 +2396,7 @@
       <c r="A15" s="93" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="132" t="n"/>
+      <c r="B15" s="227" t="n"/>
       <c r="C15" s="129" t="n"/>
       <c r="D15" s="120" t="n"/>
       <c r="E15" s="130" t="n"/>
@@ -2409,7 +2432,7 @@
       <c r="A16" s="93" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="132" t="n"/>
+      <c r="B16" s="227" t="n"/>
       <c r="C16" s="129" t="n"/>
       <c r="D16" s="120" t="n"/>
       <c r="E16" s="130" t="n"/>
@@ -2445,7 +2468,7 @@
       <c r="A17" s="93" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="132" t="n"/>
+      <c r="B17" s="227" t="n"/>
       <c r="C17" s="129" t="n"/>
       <c r="D17" s="120" t="n"/>
       <c r="E17" s="130" t="n"/>
@@ -2481,7 +2504,7 @@
       <c r="A18" s="93" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="132" t="n"/>
+      <c r="B18" s="227" t="n"/>
       <c r="C18" s="129" t="n"/>
       <c r="D18" s="120" t="n"/>
       <c r="E18" s="130" t="n"/>
@@ -2517,7 +2540,7 @@
       <c r="A19" s="93" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="132" t="n"/>
+      <c r="B19" s="227" t="n"/>
       <c r="C19" s="129" t="n"/>
       <c r="D19" s="120" t="n"/>
       <c r="E19" s="130" t="n"/>
@@ -2553,7 +2576,7 @@
       <c r="A20" s="93" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="132" t="n"/>
+      <c r="B20" s="227" t="n"/>
       <c r="C20" s="129" t="n"/>
       <c r="D20" s="120" t="n"/>
       <c r="E20" s="130" t="n"/>
@@ -2589,7 +2612,7 @@
       <c r="A21" s="93" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="132" t="n"/>
+      <c r="B21" s="227" t="n"/>
       <c r="C21" s="129" t="n"/>
       <c r="D21" s="120" t="n"/>
       <c r="E21" s="130" t="n"/>
@@ -2625,7 +2648,7 @@
       <c r="A22" s="93" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="132" t="n"/>
+      <c r="B22" s="227" t="n"/>
       <c r="C22" s="129" t="n"/>
       <c r="D22" s="120" t="n"/>
       <c r="E22" s="130" t="n"/>
@@ -2659,7 +2682,7 @@
     </row>
     <row r="23" ht="27" customHeight="1" s="92">
       <c r="A23" s="93" t="n"/>
-      <c r="B23" s="140" t="n"/>
+      <c r="B23" s="228" t="n"/>
       <c r="C23" s="141" t="n"/>
       <c r="D23" s="142" t="n"/>
       <c r="E23" s="143" t="n"/>
@@ -3278,13 +3301,13 @@
     </row>
     <row r="43" ht="27" customHeight="1" s="92">
       <c r="A43" s="93" t="n"/>
-      <c r="B43" s="200" t="inlineStr">
+      <c r="B43" s="183" t="inlineStr">
         <is>
           <t>⑥ 差額(⑤ − ④)</t>
         </is>
       </c>
       <c r="C43" s="93" t="n"/>
-      <c r="D43" s="201">
+      <c r="D43" s="221">
         <f>D42-D41</f>
         <v/>
       </c>
